--- a/발주서-웹서비스/backend/templates/밤호박_통합_소싱현황_원본.xlsx
+++ b/발주서-웹서비스/backend/templates/밤호박_통합_소싱현황_원본.xlsx
@@ -1500,7 +1500,7 @@
         <v/>
       </c>
       <c r="H8" s="85" t="n">
-        <v>7400</v>
+        <v>9800</v>
       </c>
       <c r="I8" s="50" t="n">
         <v>4900</v>
@@ -1581,7 +1581,7 @@
         <v/>
       </c>
       <c r="H9" s="85" t="n">
-        <v>15800</v>
+        <v>13700</v>
       </c>
       <c r="I9" s="50" t="n">
         <v>8050</v>
@@ -1662,7 +1662,7 @@
         <v/>
       </c>
       <c r="H10" s="85" t="n">
-        <v>19800</v>
+        <v>20700</v>
       </c>
       <c r="I10" s="52" t="n">
         <v>10250</v>
